--- a/Dia 11-Crear un Buscador/Búsquedas+con+Resultados+Múltiples.xlsx
+++ b/Dia 11-Crear un Buscador/Búsquedas+con+Resultados+Múltiples.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUSTAVO\Documents\Cursos Udemy\ExcelTotal\Dia 11-Crear un Buscador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620B8036-B064-4963-90FA-34C4D9BE20A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C65F875-FFBA-4B83-A70B-E52CFCB92AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FC8081CE-A271-46BD-87DF-D7C728F580F6}"/>
   </bookViews>
